--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999A6A28-3961-AF4E-B2CA-190BBE196E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF5ACC5-0397-8F4A-B410-29775A62A9B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$10</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -49,6 +49,9 @@
     <t>description</t>
   </si>
   <si>
+    <t>image</t>
+  </si>
+  <si>
     <t>Multimodal Conversational AI Agents Towards Smarter Assistant</t>
   </si>
   <si>
@@ -59,9 +62,6 @@
   </si>
   <si>
     <t>Microsoft Research</t>
-  </si>
-  <si>
-    <t>02/07/2024</t>
   </si>
   <si>
     <t>Cambridge, United Kingdom</t>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>Utrecht University</t>
-  </si>
-  <si>
-    <t>12/04/2023</t>
   </si>
   <si>
     <t>Utrecht, Netherlans</t>
@@ -157,9 +154,6 @@
     <t>Microsoft Research AI4Science</t>
   </si>
   <si>
-    <t>04/06/2023</t>
-  </si>
-  <si>
     <t>Amsterdam, Netherlands</t>
   </si>
   <si>
@@ -196,9 +190,6 @@
     <t>University College London (UCL)</t>
   </si>
   <si>
-    <t>07/06/2022</t>
-  </si>
-  <si>
     <t>London, UK</t>
   </si>
   <si>
@@ -247,6 +238,9 @@
     <t>ACL SIG-FinTedh x TFAI Webinar Series</t>
   </si>
   <si>
+    <t>29/03/2026</t>
+  </si>
+  <si>
     <t>Online</t>
   </si>
   <si>
@@ -286,7 +280,13 @@
     <t>Multimodal AI agents are evolving into systems capable of understanding text, vision, and spatial environments while collaborating directly with humans. This talk explores how we should evaluate these agents through through two complementary perspectives: model performance - how effectively they reason, perceive, and execute complex tasks and user experience - how they influence human creativity, learning, and well-being. Through applications in mixed reality guidance, physical assembly benchmarking, virtual co-building, and gaze interpretation, we examine the opportunities and limitations of current multimodal systems. Although these agents show strong potential for transforming learning and creativity across virtual and physical environments, advances in spatial reasoning and long-horizon task execution are still needed before they can become reliable real-world assistants.</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>/images/talks/kli2026.jpg</t>
+  </si>
+  <si>
+    <t>/images/talks/finai2026.png</t>
+  </si>
+  <si>
+    <t>/images/talks/kul2025.jpg</t>
   </si>
 </sst>
 </file>
@@ -294,7 +294,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -362,21 +362,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -681,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
@@ -690,11 +687,11 @@
     <col min="4" max="4" width="35" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="35" customWidth="1"/>
-    <col min="8" max="8" width="70" customWidth="1"/>
+    <col min="7" max="7" width="70" customWidth="1"/>
+    <col min="8" max="9" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -714,326 +711,352 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4">
+        <v>44748</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+    </row>
+    <row r="5" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="4">
+        <v>45022</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="4">
+        <v>45264</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E10" s="4">
+        <v>45329</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3" t="s">
+      <c r="G10" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="4">
+        <v>46361</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="5">
-        <v>46361</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="3" t="s">
-        <v>85</v>
-      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:H10" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H10">
+      <sortCondition descending="1" ref="E1:E10"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A443A12-D052-6B4C-8B9C-730B8CF0317C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA9D30-DAA7-FE4C-B387-56A03EB3AAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="98">
   <si>
     <t>title</t>
   </si>
@@ -317,6 +317,9 @@
 First, I will showcase a series of conversational AI agents developed through both published and ongoing research projects focused on enhancing human well-being across diverse application domains. These case studies will highlight practical lessons for designing and evaluating trustworthy AI systems that balance technical performance with human-centered outcomes.
 Second, I will introduce our research group's current interests and future directions, as well as the vision and initiatives of the AI programme within the education committee (OLC).
 Together, these efforts highlight opportunities to advance responsible, impactful, and human-centered AI for both learning and research.</t>
+  </si>
+  <si>
+    <t>Invited 'Meet the Jury' Talk</t>
   </si>
 </sst>
 </file>
@@ -690,7 +693,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="59" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" style="3" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" style="3"/>
     <col min="4" max="4" width="56.33203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.1640625" style="3" customWidth="1"/>
@@ -941,7 +944,7 @@
         <v>65</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>66</v>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DA9D30-DAA7-FE4C-B387-56A03EB3AAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A18EDD-FB50-DE44-A764-1236F7BF2212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
   <si>
     <t>title</t>
   </si>
@@ -320,13 +320,16 @@
   </si>
   <si>
     <t>Invited 'Meet the Jury' Talk</t>
+  </si>
+  <si>
+    <t>https://set.kuleuven.be/phd/seminars/pei</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +342,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -373,10 +384,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -387,8 +399,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -700,7 +716,8 @@
     <col min="6" max="6" width="23" style="3" customWidth="1"/>
     <col min="7" max="7" width="54.83203125" style="3" customWidth="1"/>
     <col min="8" max="8" width="32.83203125" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="8.83203125" style="3"/>
+    <col min="9" max="9" width="35.83203125" style="3" customWidth="1"/>
+    <col min="10" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -964,6 +981,9 @@
       <c r="H11" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="I11" s="4" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="160" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -1064,6 +1084,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I11" r:id="rId1" xr:uid="{1AFE571B-2703-D743-8EB3-2146460BF130}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A18EDD-FB50-DE44-A764-1236F7BF2212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12554E4D-883A-BA42-894D-2AEDDCA815E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="26240" windowHeight="15520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -841,7 +841,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="409.6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="409" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>34</v>
       </c>

--- a/markdown_generator/talks.xlsx
+++ b/markdown_generator/talks.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jiahuanpei/Code/Jiahuan-Pei.github.io/markdown_generator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12554E4D-883A-BA42-894D-2AEDDCA815E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6A89D5-0F04-7647-90B5-084F096BD9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="101">
   <si>
     <t>title</t>
   </si>
@@ -323,6 +323,12 @@
   </si>
   <si>
     <t>https://set.kuleuven.be/phd/seminars/pei</t>
+  </si>
+  <si>
+    <t>/images/talks/icmr2026.jpeg</t>
+  </si>
+  <si>
+    <t>/images/talks/hack4her2026.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1059,6 +1065,9 @@
       <c r="G14" s="1" t="s">
         <v>91</v>
       </c>
+      <c r="H14" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="288" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -1081,6 +1090,9 @@
       </c>
       <c r="G15" s="1" t="s">
         <v>96</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
